--- a/textbook_examples/mod01_conditional.xlsx
+++ b/textbook_examples/mod01_conditional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B8715FB-2E99-954B-814A-3C40060B914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{0B8715FB-2E99-954B-814A-3C40060B914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77AAF20-6382-6C48-9628-02C1E0016A22}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Conditional functions</t>
   </si>
@@ -107,13 +107,7 @@
     <t>How many yields above 60?</t>
   </si>
   <si>
-    <t>Average wheat yield over 250 ac</t>
-  </si>
-  <si>
-    <t>How many above the average?</t>
-  </si>
-  <si>
-    <t>The last one is the awkward case: the threshold is itself a calculation, so you glue "&gt;" onto it with &amp;.  Quoting the whole thing as "&gt;AVERAGE(...)" would search for that literal text.</t>
+    <t>Average wheat yield in fields over 250 acres</t>
   </si>
 </sst>
 </file>
@@ -220,9 +214,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,15 +525,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="1" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -755,123 +751,99 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="11"/>
+      <c r="C15" s="7">
         <f>COUNTIF(B5:B12,"Canola")</f>
         <v>3</v>
       </c>
-      <c r="C15" s="12" t="str">
-        <f t="shared" ref="C15:C20" ca="1" si="2">_xlfn.FORMULATEXT(B15)</f>
+      <c r="D15" s="12" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C15)</f>
         <v>=COUNTIF(B5:B12,"Canola")</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="11"/>
+      <c r="C16" s="7">
         <f>SUMIF(B5:B12,"Canola",C5:C12)</f>
         <v>650</v>
       </c>
-      <c r="C16" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D16" s="12" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C16)</f>
         <v>=SUMIF(B5:B12,"Canola",C5:C12)</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="11"/>
+      <c r="C17" s="7">
         <f>AVERAGEIF(B5:B12,"Canola",D5:D12)</f>
         <v>41.3</v>
       </c>
-      <c r="C17" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D17" s="12" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C17)</f>
         <v>=AVERAGEIF(B5:B12,"Canola",D5:D12)</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="11"/>
+      <c r="C18" s="7">
         <f>COUNTIF(D5:D12,"&gt;60")</f>
         <v>3</v>
       </c>
-      <c r="C18" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D18" s="12" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C18)</f>
         <v>=COUNTIF(D5:D12,"&gt;60")</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="13"/>
+      <c r="C19" s="7">
         <f>AVERAGEIFS(D5:D12,B5:B12,"Wheat",C5:C12,"&gt;250")</f>
         <v>58.25</v>
       </c>
-      <c r="C19" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D19" s="12" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C19)</f>
         <v>=AVERAGEIFS(D5:D12,B5:B12,"Wheat",C5:C12,"&gt;250")</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="7">
-        <f>COUNTIF(D5:D12,"&gt;"&amp;AVERAGE(D5:D12))</f>
-        <v>5</v>
-      </c>
-      <c r="C20" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>=COUNTIF(D5:D12,"&gt;"&amp;AVERAGE(D5:D12))</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C19:F19"/>
+  <mergeCells count="11">
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/textbook_examples/mod01_conditional.xlsx
+++ b/textbook_examples/mod01_conditional.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{0B8715FB-2E99-954B-814A-3C40060B914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77AAF20-6382-6C48-9628-02C1E0016A22}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{0B8715FB-2E99-954B-814A-3C40060B914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC838996-66AE-6743-97F4-59EFA2ECF89B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Conditional" sheetId="1" r:id="rId1"/>
+    <sheet name="Complete" sheetId="1" r:id="rId1"/>
+    <sheet name="Incomplete" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
-  <si>
-    <t>Conditional functions</t>
-  </si>
-  <si>
-    <t>Eight fields, each with a crop and a yield.  The functions below all answer questions about a SUBSET of the rows — only the canola fields, only the yields above a threshold.  Column F shows the formula that produced column E.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="24">
   <si>
     <t>Field</t>
   </si>
@@ -108,6 +103,27 @@
   </si>
   <si>
     <t>Average wheat yield in fields over 250 acres</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF5C6B62"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Explanation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF5C6B62"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The data has eight fields, each with a crop and a yield.  The functions below all answer questions about a SUBSET of the rows — only the canola fields, only the yields above a threshold.  Column F shows the formula that produced column E.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -117,7 +133,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,12 +145,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF4A7C59"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF5C6B62"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -164,6 +174,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF5C6B62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF5C6B62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -190,39 +213,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,75 +557,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>320</v>
+      </c>
+      <c r="D2" s="7">
+        <v>41.2</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <f t="shared" ref="E2:E8" si="0">IF(D2&gt;50,"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="F2" s="8" t="str">
+        <f t="shared" ref="F2:F9" ca="1" si="1">_xlfn.FORMULATEXT(E2)</f>
+        <v>=IF(D2&gt;50,"Yes","No")</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6">
+        <v>250</v>
+      </c>
+      <c r="D3" s="7">
+        <v>58.6</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="F3" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>=IF(D3&gt;50,"Yes","No")</v>
+      </c>
+    </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="C4" s="6">
+        <v>180</v>
+      </c>
+      <c r="D4" s="7">
+        <v>37.9</v>
+      </c>
+      <c r="E4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="F4" s="8" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>=IF(D4&gt;50,"Yes","No")</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="6">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="D5" s="7">
-        <v>41.2</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="E5" s="5" t="str">
-        <f t="shared" ref="E5:E12" si="0">IF(D5&gt;50,"Yes","No")</f>
-        <v>No</v>
+        <f t="shared" si="0"/>
+        <v>Yes</v>
       </c>
       <c r="F5" s="8" t="str">
-        <f t="shared" ref="F5:F12" ca="1" si="1">_xlfn.FORMULATEXT(E5)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>=IF(D5&gt;50,"Yes","No")</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="D6" s="7">
-        <v>58.6</v>
+        <v>61.3</v>
       </c>
       <c r="E6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -614,16 +688,16 @@
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D7" s="7">
-        <v>37.9</v>
+        <v>44.8</v>
       </c>
       <c r="E7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -636,16 +710,16 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="D8" s="7">
-        <v>72.400000000000006</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="E8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -658,19 +732,19 @@
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="D9" s="7">
-        <v>61.3</v>
+        <v>55.2</v>
       </c>
       <c r="E9" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D9&gt;50,"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="F9" s="8" t="str">
@@ -678,172 +752,343 @@
         <v>=IF(D9&gt;50,"Yes","No")</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>150</v>
-      </c>
-      <c r="D10" s="7">
-        <v>44.8</v>
-      </c>
-      <c r="E10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>No</v>
-      </c>
-      <c r="F10" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>=IF(D10&gt;50,"Yes","No")</v>
-      </c>
-    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="6">
-        <v>275</v>
-      </c>
-      <c r="D11" s="7">
-        <v>68.099999999999994</v>
-      </c>
-      <c r="E11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="F11" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>=IF(D11&gt;50,"Yes","No")</v>
-      </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="6">
-        <v>330</v>
-      </c>
-      <c r="D12" s="7">
-        <v>55.2</v>
-      </c>
-      <c r="E12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Yes</v>
-      </c>
-      <c r="F12" s="8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>=IF(D12&gt;50,"Yes","No")</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="7">
+        <f>COUNTIF(B2:B9,"Canola")</f>
+        <v>3</v>
+      </c>
+      <c r="D12" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C12)</f>
+        <v>=COUNTIF(B2:B9,"Canola")</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="7">
+        <f>SUMIF(B2:B9,"Canola",C2:C9)</f>
+        <v>650</v>
+      </c>
+      <c r="D13" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C13)</f>
+        <v>=SUMIF(B2:B9,"Canola",C2:C9)</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>19</v>
-      </c>
+      <c r="A14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="7">
+        <f>AVERAGEIF(B2:B9,"Canola",D2:D9)</f>
+        <v>41.3</v>
+      </c>
+      <c r="D14" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C14)</f>
+        <v>=AVERAGEIF(B2:B9,"Canola",D2:D9)</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="11"/>
+      <c r="A15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="12"/>
       <c r="C15" s="7">
-        <f>COUNTIF(B5:B12,"Canola")</f>
+        <f>COUNTIF(D2:D9,"&gt;60")</f>
         <v>3</v>
       </c>
-      <c r="D15" s="12" t="str">
+      <c r="D15" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C15)</f>
-        <v>=COUNTIF(B5:B12,"Canola")</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="11"/>
+        <v>=COUNTIF(D2:D9,"&gt;60")</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="13"/>
       <c r="C16" s="7">
-        <f>SUMIF(B5:B12,"Canola",C5:C12)</f>
-        <v>650</v>
-      </c>
-      <c r="D16" s="12" t="str">
+        <f>AVERAGEIFS(D2:D9,B2:B9,"Wheat",C2:C9,"&gt;250")</f>
+        <v>58.25</v>
+      </c>
+      <c r="D16" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C16)</f>
-        <v>=SUMIF(B5:B12,"Canola",C5:C12)</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="7">
-        <f>AVERAGEIF(B5:B12,"Canola",D5:D12)</f>
-        <v>41.3</v>
-      </c>
-      <c r="D17" s="12" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C17)</f>
-        <v>=AVERAGEIF(B5:B12,"Canola",D5:D12)</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
+        <v>=AVERAGEIFS(D2:D9,B2:B9,"Wheat",C2:C9,"&gt;250")</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="7">
-        <f>COUNTIF(D5:D12,"&gt;60")</f>
-        <v>3</v>
-      </c>
-      <c r="D18" s="12" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C18)</f>
-        <v>=COUNTIF(D5:D12,"&gt;60")</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="7">
-        <f>AVERAGEIFS(D5:D12,B5:B12,"Wheat",C5:C12,"&gt;250")</f>
-        <v>58.25</v>
-      </c>
-      <c r="D19" s="12" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C19)</f>
-        <v>=AVERAGEIFS(D5:D12,B5:B12,"Wheat",C5:C12,"&gt;250")</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E69CA5-BF75-1842-9DE4-547EC15BB3C1}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>320</v>
+      </c>
+      <c r="D2" s="7">
+        <v>41.2</v>
+      </c>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6">
+        <v>250</v>
+      </c>
+      <c r="D3" s="7">
+        <v>58.6</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6">
+        <v>180</v>
+      </c>
+      <c r="D4" s="7">
+        <v>37.9</v>
+      </c>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6">
+        <v>210</v>
+      </c>
+      <c r="D5" s="7">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="6">
+        <v>400</v>
+      </c>
+      <c r="D6" s="7">
+        <v>61.3</v>
+      </c>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6">
+        <v>150</v>
+      </c>
+      <c r="D7" s="7">
+        <v>44.8</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6">
+        <v>275</v>
+      </c>
+      <c r="D8" s="7">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>330</v>
+      </c>
+      <c r="D9" s="7">
+        <v>55.2</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/textbook_examples/mod01_conditional.xlsx
+++ b/textbook_examples/mod01_conditional.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{0B8715FB-2E99-954B-814A-3C40060B914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC838996-66AE-6743-97F4-59EFA2ECF89B}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{0B8715FB-2E99-954B-814A-3C40060B914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD1F511D-E83B-EF43-A0C0-8CB0E8AB4F01}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete" sheetId="1" r:id="rId1"/>
-    <sheet name="Incomplete" sheetId="2" r:id="rId2"/>
+    <sheet name="Practice" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="26">
   <si>
     <t>Field</t>
   </si>
@@ -124,6 +124,12 @@
       </rPr>
       <t xml:space="preserve"> The data has eight fields, each with a crop and a yield.  The functions below all answer questions about a SUBSET of the rows — only the canola fields, only the yields above a threshold.  Column F shows the formula that produced column E.</t>
     </r>
+  </si>
+  <si>
+    <t>&lt;- Set this cell equal to "Yes" if yields are above 50 and "No" if not</t>
+  </si>
+  <si>
+    <t>Total acres in fields with acres&gt;300</t>
   </si>
 </sst>
 </file>
@@ -213,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -246,7 +252,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,13 +882,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E69CA5-BF75-1842-9DE4-547EC15BB3C1}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -896,7 +905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -910,8 +919,11 @@
         <v>41.2</v>
       </c>
       <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -926,7 +938,7 @@
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -941,7 +953,7 @@
       </c>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -956,7 +968,7 @@
       </c>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
@@ -971,7 +983,7 @@
       </c>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -986,7 +998,7 @@
       </c>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -1001,7 +1013,7 @@
       </c>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -1016,58 +1028,62 @@
       </c>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-    </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="15"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="15"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="15"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="7"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
     </row>

--- a/textbook_examples/mod01_conditional.xlsx
+++ b/textbook_examples/mod01_conditional.xlsx
@@ -240,11 +240,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -252,9 +250,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,12 +776,12 @@
         <f>COUNTIF(B2:B9,"Canola")</f>
         <v>3</v>
       </c>
-      <c r="D12" s="10" t="str">
+      <c r="D12" s="15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C12)</f>
         <v>=COUNTIF(B2:B9,"Canola")</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
@@ -792,12 +792,12 @@
         <f>SUMIF(B2:B9,"Canola",C2:C9)</f>
         <v>650</v>
       </c>
-      <c r="D13" s="10" t="str">
+      <c r="D13" s="15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C13)</f>
         <v>=SUMIF(B2:B9,"Canola",C2:C9)</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
@@ -808,12 +808,12 @@
         <f>AVERAGEIF(B2:B9,"Canola",D2:D9)</f>
         <v>41.3</v>
       </c>
-      <c r="D14" s="10" t="str">
+      <c r="D14" s="15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C14)</f>
         <v>=AVERAGEIF(B2:B9,"Canola",D2:D9)</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
@@ -824,12 +824,12 @@
         <f>COUNTIF(D2:D9,"&gt;60")</f>
         <v>3</v>
       </c>
-      <c r="D15" s="10" t="str">
+      <c r="D15" s="15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C15)</f>
         <v>=COUNTIF(D2:D9,"&gt;60")</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
@@ -840,26 +840,26 @@
         <f>AVERAGEIFS(D2:D9,B2:B9,"Wheat",C2:C9,"&gt;250")</f>
         <v>58.25</v>
       </c>
-      <c r="D16" s="10" t="str">
+      <c r="D16" s="15" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C16)</f>
         <v>=AVERAGEIFS(D2:D9,B2:B9,"Wheat",C2:C9,"&gt;250")</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:6" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -1039,7 +1039,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
@@ -1048,7 +1048,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
@@ -1066,7 +1066,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="14"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1088,13 +1088,13 @@
       <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:5" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/textbook_examples/mod01_conditional.xlsx
+++ b/textbook_examples/mod01_conditional.xlsx
@@ -240,9 +240,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -250,11 +252,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,12 +776,12 @@
         <f>COUNTIF(B2:B9,"Canola")</f>
         <v>3</v>
       </c>
-      <c r="D12" s="15" t="str">
+      <c r="D12" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C12)</f>
         <v>=COUNTIF(B2:B9,"Canola")</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
@@ -792,12 +792,12 @@
         <f>SUMIF(B2:B9,"Canola",C2:C9)</f>
         <v>650</v>
       </c>
-      <c r="D13" s="15" t="str">
+      <c r="D13" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C13)</f>
         <v>=SUMIF(B2:B9,"Canola",C2:C9)</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
@@ -808,12 +808,12 @@
         <f>AVERAGEIF(B2:B9,"Canola",D2:D9)</f>
         <v>41.3</v>
       </c>
-      <c r="D14" s="15" t="str">
+      <c r="D14" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C14)</f>
         <v>=AVERAGEIF(B2:B9,"Canola",D2:D9)</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
@@ -824,12 +824,12 @@
         <f>COUNTIF(D2:D9,"&gt;60")</f>
         <v>3</v>
       </c>
-      <c r="D15" s="15" t="str">
+      <c r="D15" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C15)</f>
         <v>=COUNTIF(D2:D9,"&gt;60")</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
@@ -840,26 +840,26 @@
         <f>AVERAGEIFS(D2:D9,B2:B9,"Wheat",C2:C9,"&gt;250")</f>
         <v>58.25</v>
       </c>
-      <c r="D16" s="15" t="str">
+      <c r="D16" s="10" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C16)</f>
         <v>=AVERAGEIFS(D2:D9,B2:B9,"Wheat",C2:C9,"&gt;250")</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:6" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -1039,7 +1039,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="11"/>
+      <c r="C12" s="15"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
@@ -1048,7 +1048,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="11"/>
+      <c r="C13" s="15"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
@@ -1066,7 +1066,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="11"/>
+      <c r="C15" s="15"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="10"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1088,13 +1088,13 @@
       <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:5" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
